--- a/MIPI_deployment.xlsx
+++ b/MIPI_deployment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cyril.germaine\Documents\work\projets\mipi_linux_rpi_eg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cyril.germaine\Documents\work\projets\MIPI\mipi_linux_rpi_eg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0326770-AA44-4B43-929A-F7E218B6D4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB5D4D5-F40E-4B03-91E7-46929F68A998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D61E0E21-A3C2-41B9-A323-5A81E21B33EC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{D61E0E21-A3C2-41B9-A323-5A81E21B33EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Raspberry Pi" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
   <si>
     <t>OK*</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Bullseye</t>
-  </si>
-  <si>
-    <t>Bookworm </t>
   </si>
   <si>
     <t>6.5.0-1005
@@ -104,9 +101,6 @@
   </si>
   <si>
     <t>Linux kernel versions **</t>
-  </si>
-  <si>
-    <t>** For Bookworm and Ubuntu, any other kernel version will not support Y16 without driver upgrade</t>
   </si>
   <si>
     <t>Rpi4</t>
@@ -149,14 +143,29 @@
     <t>Not supported</t>
   </si>
   <si>
-    <t>2023-12-05 6.1.0-rpi7-rpi-v8
-2024-03-15 6.6.20+rpt-rpi-v8
-2024-07-04 6.6.31+rpt-rpi-v8
-2025-13-05 6.12.25+rpt-rpi-v8</t>
-  </si>
-  <si>
-    <t>2024-07-04 6.6.31+rpt-rpi-2712
-2025-13-05 6.12.25+rpt-rpi-2712</t>
+    <t>Bookworm, Trixie</t>
+  </si>
+  <si>
+    <t>2023-12-05 6.1.0
+2024-03-15 6.6.20
+2024-07-04 6.6.31
+2025-13-05 6.12.25
+2025-12-04 6.12.47
+2026-04-21 6.12.75
+6.18.29</t>
+  </si>
+  <si>
+    <t>2024-07-04 6.6.31
+2025-13-05 6.12.25
+2025-12-04 6.12.47
+2026-04-21 6.12.75
+6.18.29</t>
+  </si>
+  <si>
+    <t>Bookworm/Trixie</t>
+  </si>
+  <si>
+    <t>** For Bookworm/Trixie and Ubuntu, any other kernel version will not support Y16 without driver patches</t>
   </si>
 </sst>
 </file>
@@ -873,7 +882,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -885,36 +894,36 @@
         <v>13</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -989,10 +998,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1015,10 +1024,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1041,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1060,7 +1069,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -1096,46 +1105,46 @@
     <row r="1" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1148,21 +1157,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ddfcbff1-988c-4780-af66-42272a7444f2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5eab2033-26a9-4886-8f5a-efa3f46bf7e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="ddfcbff1-988c-4780-af66-42272a7444f2">
-      <UserInfo>
-        <DisplayName>Cyril Germaine</DisplayName>
-        <AccountId>370</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1421,27 +1421,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ddfcbff1-988c-4780-af66-42272a7444f2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5eab2033-26a9-4886-8f5a-efa3f46bf7e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="ddfcbff1-988c-4780-af66-42272a7444f2">
+      <UserInfo>
+        <DisplayName>Cyril Germaine</DisplayName>
+        <AccountId>370</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CC26F4-9ACA-496B-B719-4372C9693134}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21273CB7-CC8A-48C1-BA2A-0CD67C70C578}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="5eab2033-26a9-4886-8f5a-efa3f46bf7e3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="ddfcbff1-988c-4780-af66-42272a7444f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1466,9 +1466,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21273CB7-CC8A-48C1-BA2A-0CD67C70C578}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6CC26F4-9ACA-496B-B719-4372C9693134}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ddfcbff1-988c-4780-af66-42272a7444f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5eab2033-26a9-4886-8f5a-efa3f46bf7e3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>